--- a/data/fullyear-resilience/Power_WeightsRP.xlsx
+++ b/data/fullyear-resilience/Power_WeightsRP.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\fullyear-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90148D15-EFB6-4ED1-963F-1CEDDBD25B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46B097F-6AB0-4CE1-8FD1-0C93229930E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
+    <sheet name="year2017" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -99,8 +100,88 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{A760C4CE-71B4-4518-8B7A-2D342AFE6127}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Readable name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{25A8E4B1-09F4-4F3C-8FA3-DB70A371FCAA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Value specifier in database</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{AB69ADCA-DF5B-4532-A0AF-67B8F4B3FB1E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Description</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{69E7C94C-009D-4F87-8046-B4840BC1E72F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Details on database behavior</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{A2C4F315-748F-4D2F-8154-E60B989E71F6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Unit or valid values</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="28">
   <si>
     <t>Power - Weights of representative periods</t>
   </si>
@@ -790,4 +871,185 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273D6B2D-5208-4B04-82CE-9B41AB306311}">
+  <sheetPr>
+    <tabColor rgb="FF008080"/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="6" width="24.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="10"/>
+      <c r="C8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="12">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>